--- a/TMS_PCMs.xlsx
+++ b/TMS_PCMs.xlsx
@@ -972,7 +972,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Dispatched</t>
+          <t>Request Resolved</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
